--- a/Transit Time/V5_Transit_Time_Analysis.xlsx
+++ b/Transit Time/V5_Transit_Time_Analysis.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">V5 Logistics – Transit-Time Analysis Workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Bhiwandi–Kolhapur Mini-Hub Assessment | Prepared by Sambhav, Part-time Intern | Route validation date: 23 October 2026</t>
+    <t xml:space="preserve">Bhiwandi–Kolhapur Mini-Hub Assessment | Prepared by Mahir Valani | Route validation date: 23 October 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Colour legend: BLUE text on light-blue fill = source input (hours and minutes entered as recorded). BLACK text on grey fill = calculated by formula. YELLOW = analyst-selected scenario assumption.</t>
